--- a/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T05:55:59+00:00</t>
+    <t>2026-10-01T06:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
+++ b/ci-build/ValueSet-onko-behandlungsmodalitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
